--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>12797400</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>23100</v>
+        <v>23142</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>12797400</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>23100</v>
+        <v>23142</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -39465,9 +39465,9 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1280万
-$23,100/呎
+$23,142/呎
 (26年-06月-17日)</t>
         </is>
       </c>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>13185200</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>23800</v>
+        <v>23843</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>13185200</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>23800</v>
+        <v>23843</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>12951000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>23377</v>
+        <v>23420</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>12951000</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>23377</v>
+        <v>23420</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -39270,9 +39270,9 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1319万
-$23,800/呎
+$23,843/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -39777,9 +39777,9 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1295万
-$23,377/呎
+$23,420/呎
 (26年-06月-22日)</t>
         </is>
       </c>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -16010,14 +16010,14 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
         <v>11591000</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>20922</v>
+        <v>20960</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>11591000</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>20922</v>
+        <v>20960</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -40128,10 +40128,10 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1159万
-$20,922/呎
-(26年-08月-18日)</t>
+$20,960/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>38686000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>29000</v>
+        <v>28978</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>38686000</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>29000</v>
+        <v>28978</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>12354200</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>22300</v>
+        <v>22340</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>12354200</v>
       </c>
       <c r="L219" s="5" t="n">
-        <v>22300</v>
+        <v>22340</v>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
@@ -15261,34 +15261,34 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
-        <v>13112300</v>
+        <v>11801000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>23668</v>
+        <v>21301</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>11801070</v>
+        <v>11801000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>21302</v>
+        <v>21301</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -38905,7 +38905,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38915,7 +38915,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -38972,9 +38972,9 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>B | 1334呎 (3房)
+          <t>B | 1335呎 (3房)
 $3869万
-$29,000/呎
+$28,978/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -39894,9 +39894,9 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1235万
-$22,300/呎
+$22,340/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -40009,12 +40009,12 @@
 (25年-08月-27日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
-$1311万
-$23,668/呎
-(在售)</t>
+$1180万
+$21,301/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2088</v>
+        <v>2034</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>91265500</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>43710</v>
+        <v>44870</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>91265500</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>43710</v>
+        <v>44870</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -9231,34 +9231,34 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>13908900</v>
+        <v>12518000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>27326</v>
+        <v>24593</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>12518010</v>
+        <v>12518000</v>
       </c>
       <c r="L134" s="5" t="n">
         <v>24593</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -15509,34 +15509,34 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>12913400</v>
+        <v>11622000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>23309</v>
+        <v>20978</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>11622060</v>
+        <v>11622000</v>
       </c>
       <c r="L235" s="5" t="n">
         <v>20978</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
@@ -15757,34 +15757,34 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
-        <v>12835600</v>
+        <v>11552000</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>23169</v>
+        <v>20852</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>11552040</v>
+        <v>11552000</v>
       </c>
       <c r="L239" s="5" t="n">
         <v>20852</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -37971,9 +37971,9 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>A | 2088呎 (4+房)
+          <t>A | 2034呎 (4+房)
 $9127万
-$43,710/呎
+$44,870/呎
 (23年-03月-15日)</t>
         </is>
       </c>
@@ -38905,17 +38905,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39081,12 +39081,12 @@
 (26年-09月-03日)</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1391万
-$27,326/呎
-(已定价未售)</t>
+$1252万
+$24,593/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
@@ -40048,12 +40048,12 @@
 (25年-09月-01日)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
-$1291万
-$23,309/呎
-(已定价未售)</t>
+$1162万
+$20,978/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
@@ -40087,12 +40087,12 @@
 (25年-09月-22日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 554呎 (2房)
-$1284万
-$23,169/呎
-(在售)</t>
+$1155万
+$20,852/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>11552000</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>20852</v>
+        <v>20890</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>11552000</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>20852</v>
+        <v>20890</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -40089,9 +40089,9 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1155万
-$20,852/呎
+$20,890/呎
 (26年-09月-18日)</t>
         </is>
       </c>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -9169,7 +9169,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -11471,34 +11471,34 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>13417800</v>
+        <v>12076000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>26361</v>
+        <v>23725</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>12076020</v>
+        <v>12076000</v>
       </c>
       <c r="L170" s="5" t="n">
         <v>23725</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>180天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -37047,7 +37047,7 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -37057,12 +37057,12 @@
       </c>
       <c r="H582" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I582" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J582" s="3" t="inlineStr">
@@ -37072,12 +37072,12 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M582" s="3" t="inlineStr">
@@ -37087,7 +37087,7 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37117,7 +37117,7 @@
       </c>
       <c r="F583" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G583" s="3" t="inlineStr">
@@ -37127,12 +37127,12 @@
       </c>
       <c r="H583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J583" s="3" t="inlineStr">
@@ -37142,12 +37142,12 @@
       </c>
       <c r="K583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M583" s="3" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="N583" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38905,17 +38905,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -38925,7 +38925,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -39065,12 +39065,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -39089,12 +39089,12 @@
 (26年-09月-21日)</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $913万
 $24,603/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39276,15 +39276,54 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1363万
 $26,787/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 371呎 (1房)
+$904万
+$24,358/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 577呎 (2房)
+$1469万
+$25,454/呎
+(24年-10月-29日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 553呎 (2房)
+$1285万
+$23,242/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 509呎 (2房)
+$1196万
+$23,500/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>D | 371呎 (1房)
 $904万
@@ -39293,45 +39332,6 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>A | 577呎 (2房)
-$1469万
-$25,454/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>B | 553呎 (2房)
-$1285万
-$23,242/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>C | 509呎 (2房)
-$1196万
-$23,500/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>D | 371呎 (1房)
-$904万
-$24,358/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
@@ -39432,12 +39432,12 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1342万
-$26,361/呎
-(在售)</t>
+$1208万
+$23,725/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -39471,12 +39471,12 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1336万
 $26,256/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -39510,12 +39510,12 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1331万
 $26,152/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
@@ -39627,12 +39627,12 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1315万
 $25,842/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
@@ -39666,12 +39666,12 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
 $1315万
 $25,842/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
@@ -44231,14 +44231,14 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
       <c r="D3" s="29" t="inlineStr">
         <is>
           <t>2 套</t>
@@ -44246,12 +44246,12 @@
       </c>
       <c r="E3" s="30" t="inlineStr">
         <is>
-          <t>2 套</t>
+          <t>1 套</t>
         </is>
       </c>
       <c r="F3" s="26" t="inlineStr">
         <is>
-          <t>2 套</t>
+          <t>1 套</t>
         </is>
       </c>
     </row>
@@ -44321,13 +44321,13 @@
       </c>
       <c r="B8" s="31" t="inlineStr"/>
       <c r="C8" s="31" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Mansion C (Harbour Wave)
 4850呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+(在售)
+招标项目
+-</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -33076,14 +33076,14 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
-        <v>162236000</v>
+        <v>167436000</v>
       </c>
       <c r="I518" s="5" t="n">
-        <v>61476</v>
+        <v>63447</v>
       </c>
       <c r="J518" s="3" t="inlineStr">
         <is>
@@ -33091,10 +33091,10 @@
         </is>
       </c>
       <c r="K518" s="5" t="n">
-        <v>162236000</v>
+        <v>167436000</v>
       </c>
       <c r="L518" s="5" t="n">
-        <v>61476</v>
+        <v>63447</v>
       </c>
       <c r="M518" s="3" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         </is>
       </c>
       <c r="E569" s="4" t="n">
-        <v>1185</v>
+        <v>1132</v>
       </c>
       <c r="F569" s="3" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>33000000</v>
       </c>
       <c r="I569" s="5" t="n">
-        <v>27848</v>
+        <v>29152</v>
       </c>
       <c r="J569" s="3" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>33000000</v>
       </c>
       <c r="L569" s="5" t="n">
-        <v>27848</v>
+        <v>29152</v>
       </c>
       <c r="M569" s="3" t="inlineStr">
         <is>
@@ -43463,9 +43463,9 @@
       <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 2639呎 (4+房)
-$16224万
-$61,476/呎
-(23年-09月-28日)</t>
+$16744万
+$63,447/呎
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr"/>
@@ -44061,9 +44061,9 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>B | 1185呎 (3房)
+          <t>B | 1132呎 (3房)
 $3300万
-$27,848/呎
+$29,152/呎
 (24年-04月-18日)</t>
         </is>
       </c>

--- a/九龙-启德-沄璟/沄璟_销控明细表.xlsx
+++ b/九龙-启德-沄璟/沄璟_销控明细表.xlsx
@@ -9236,7 +9236,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -15266,14 +15266,14 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
         <v>11801000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>21301</v>
+        <v>21340</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>11801000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>21301</v>
+        <v>21340</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -15514,14 +15514,14 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
         <v>11622000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>20978</v>
+        <v>21016</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>11622000</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>20978</v>
+        <v>21016</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -33687,7 +33687,7 @@
         </is>
       </c>
       <c r="E528" s="4" t="n">
-        <v>1523</v>
+        <v>1469</v>
       </c>
       <c r="F528" s="3" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>54980300</v>
       </c>
       <c r="I528" s="5" t="n">
-        <v>36100</v>
+        <v>37427</v>
       </c>
       <c r="J528" s="3" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>54980300</v>
       </c>
       <c r="L528" s="5" t="n">
-        <v>36100</v>
+        <v>37427</v>
       </c>
       <c r="M528" s="3" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
           <t>C | 509呎 (2房)
 $1252万
 $24,593/呎
-(26年-09月-21日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -40011,10 +40011,10 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1180万
-$21,301/呎
-(26年-09月-17日)</t>
+$21,340/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
@@ -40050,10 +40050,10 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 553呎 (2房)
 $1162万
-$20,978/呎
-(26年-09月-21日)</t>
+$21,016/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
@@ -40092,7 +40092,7 @@
           <t>B | 553呎 (2房)
 $1155万
 $20,890/呎
-(26年-09月-18日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -43570,9 +43570,9 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 1523呎 (3房)
+          <t>A | 1469呎 (3房)
 $5498万
-$36,100/呎
+$37,427/呎
 (24年-12月-18日)</t>
         </is>
       </c>
